--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shank\Desktop\MY PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D418497A-23A5-4C32-8780-245AEC1AEBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C7B52-6B86-48A9-BAD3-F8B3A3220F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CD8F0B71-79B1-40C9-A2D5-894CEF5A2152}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="47">
   <si>
     <t>VNMI1040185648</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>Confirmed on</t>
-  </si>
-  <si>
-    <t>Address</t>
   </si>
   <si>
     <t>Unit Holder</t>
@@ -565,15 +562,48 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -591,39 +621,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1122,28 +1119,28 @@
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="30">
       <c r="A1" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E1" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="24" t="s">
         <v>44</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>45</v>
       </c>
       <c r="G1" s="25" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I1" s="25" t="s">
         <v>2</v>
@@ -1154,28 +1151,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" s="27">
         <v>46142.435578703706</v>
       </c>
       <c r="G2" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I2" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="27">
@@ -1184,28 +1181,28 @@
         <v>VNMI1040186552</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="27">
         <v>46142.44599537037</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="27">
@@ -1214,28 +1211,28 @@
         <v>VNMI1040187456</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="27">
         <v>46142.466828703706</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="27">
@@ -1244,28 +1241,28 @@
         <v>VNMI1040188360</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="27">
         <v>46142.47724537037</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="27">
@@ -1274,28 +1271,28 @@
         <v>VNMI1040189264</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="27">
         <v>46142.484189814815</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="27">
@@ -1304,28 +1301,28 @@
         <v>VNMI1040190168</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="27">
         <v>46142.525856481479</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27">
@@ -1334,28 +1331,28 @@
         <v>VNMI1040191072</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" s="27">
         <v>46143.536273148151</v>
       </c>
       <c r="G8" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I8" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="27">
@@ -1364,28 +1361,28 @@
         <v>VNMI1040191976</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="27">
         <v>46143.557106481479</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="27">
@@ -1394,28 +1391,28 @@
         <v>VNMI1040192880</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="27">
         <v>46143.567523148151</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="27">
@@ -1424,28 +1421,28 @@
         <v>VNMI1040193784</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="27">
         <v>46143.574467592596</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="27">
@@ -1454,28 +1451,28 @@
         <v>VNMI1040194688</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" s="27">
         <v>46143.61613425926</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="27">
@@ -1484,28 +1481,28 @@
         <v>VNMI1040195592</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="27">
         <v>46143.626550925925</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="27">
@@ -1514,28 +1511,28 @@
         <v>VNMI1040196496</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="27">
         <v>46143.64738425926</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="27">
@@ -1544,28 +1541,28 @@
         <v>VNMI1040197400</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" s="27">
         <v>46143.657800925925</v>
       </c>
       <c r="G15" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I15" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="27">
@@ -1574,28 +1571,28 @@
         <v>VNMI1040198304</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16" s="27">
         <v>46143.66474537037</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27">
@@ -1604,28 +1601,28 @@
         <v>VNMI1040199208</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" s="27">
         <v>46143.706412037034</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="27">
@@ -1634,28 +1631,28 @@
         <v>VNMI1040200112</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" s="27">
         <v>46143.716828703706</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="27">
@@ -1664,28 +1661,28 @@
         <v>VNMI1040201016</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" s="27">
         <v>46144.737662037034</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27">
@@ -1694,28 +1691,28 @@
         <v>VNMI1040201920</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" s="27">
         <v>46144.748078703706</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27">
@@ -1724,28 +1721,28 @@
         <v>VNMI1040202824</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="27">
         <v>46144.755023148151</v>
       </c>
       <c r="G21" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I21" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="27">
@@ -1754,28 +1751,28 @@
         <v>VNMI1040203728</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22" s="27">
         <v>46144.796689814815</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="27">
@@ -1784,28 +1781,28 @@
         <v>VNMI1040204632</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F23" s="27">
         <v>46144.807106481479</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="27">
@@ -1814,28 +1811,28 @@
         <v>VNMI1040205536</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24" s="27">
         <v>46144.827939814815</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="27">
@@ -1844,28 +1841,28 @@
         <v>VNMI1040206440</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" s="27">
         <v>46144.838356481479</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="27">
@@ -1874,28 +1871,28 @@
         <v>VNMI1040207344</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F26" s="27">
         <v>46144.845300925925</v>
       </c>
       <c r="G26" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H26" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I26" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="27">
@@ -1904,28 +1901,28 @@
         <v>VNMI1040208248</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F27" s="27">
         <v>46144.886967592596</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="27">
@@ -1934,28 +1931,28 @@
         <v>VNMI1040209152</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F28" s="27">
         <v>46144.89738425926</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="27">
@@ -1964,28 +1961,28 @@
         <v>VNMI1040210056</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F29" s="27">
         <v>46145.918217592596</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="27">
@@ -1994,28 +1991,28 @@
         <v>VNMI1040210960</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" s="27">
         <v>46146.92863425926</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="27">
@@ -2024,28 +2021,28 @@
         <v>VNMI1040211864</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F31" s="27">
         <v>46146.935578703706</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="27">
@@ -2054,28 +2051,28 @@
         <v>VNMI1040212768</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F32" s="27">
         <v>46146.97724537037</v>
       </c>
       <c r="G32" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I32" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="27">
@@ -2084,28 +2081,28 @@
         <v>VNMI1040213672</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" s="27">
         <v>46146.987662037034</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="27">
@@ -2114,28 +2111,28 @@
         <v>VNMI1040214576</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F34" s="27">
         <v>46147.00849537037</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="27">
@@ -2144,28 +2141,28 @@
         <v>VNMI1040215480</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F35" s="27">
         <v>46147.018912037034</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="27">
@@ -2174,28 +2171,28 @@
         <v>VNMI1040216384</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F36" s="27">
         <v>46147.025856481479</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I36" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="27">
@@ -2204,28 +2201,28 @@
         <v>VNMI1040217288</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F37" s="27">
         <v>46147.067523148151</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I37" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="27">
@@ -2234,28 +2231,28 @@
         <v>VNMI1040218192</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F38" s="27">
         <v>46147.077939814815</v>
       </c>
       <c r="G38" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I38" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="27">
@@ -2264,28 +2261,28 @@
         <v>VNMI1040219096</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F39" s="27">
         <v>46147.098773148151</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27">
@@ -2294,28 +2291,28 @@
         <v>VNMI1040220000</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F40" s="27">
         <v>46147.109189814815</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="27">
@@ -2324,28 +2321,28 @@
         <v>VNMI1040220904</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F41" s="27">
         <v>46147.11613425926</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="27">
@@ -2354,28 +2351,28 @@
         <v>VNMI1040221808</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F42" s="27">
         <v>46147.157800925925</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I42" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="27">
@@ -2384,28 +2381,28 @@
         <v>VNMI1040222712</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F43" s="27">
         <v>46147.168217592596</v>
       </c>
       <c r="G43" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I43" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="27">
@@ -2414,28 +2411,28 @@
         <v>VNMI1040223616</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F44" s="27">
         <v>46147.189050925925</v>
       </c>
       <c r="G44" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I44" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="27">
@@ -2444,28 +2441,28 @@
         <v>VNMI1040224520</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F45" s="27">
         <v>46147.199467592596</v>
       </c>
       <c r="G45" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H45" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I45" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="27">
@@ -2474,28 +2471,28 @@
         <v>VNMI1040225424</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F46" s="27">
         <v>46147.206412037034</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="27">
@@ -2504,28 +2501,28 @@
         <v>VNMI1040226328</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F47" s="27">
         <v>46147.248078703706</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I47" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="27">
@@ -2534,28 +2531,28 @@
         <v>VNMI1040227232</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F48" s="27">
         <v>46147.25849537037</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I48" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="27">
@@ -2564,28 +2561,28 @@
         <v>VNMI1040228136</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F49" s="27">
         <v>46147.279328703706</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I49" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="27">
@@ -2594,28 +2591,28 @@
         <v>VNMI1040229040</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F50" s="27">
         <v>46147.28974537037</v>
       </c>
       <c r="G50" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I50" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="27">
@@ -2624,28 +2621,28 @@
         <v>VNMI1040229944</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F51" s="27">
         <v>46147.296689814815</v>
       </c>
       <c r="G51" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H51" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I51" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="27">
@@ -2654,28 +2651,28 @@
         <v>VNMI1040230848</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F52" s="27">
         <v>46147.338356481479</v>
       </c>
       <c r="G52" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I52" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="27">
@@ -2684,28 +2681,28 @@
         <v>VNMI1040231752</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F53" s="27">
         <v>46147.348773148151</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I53" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="27">
@@ -2714,28 +2711,28 @@
         <v>VNMI1040232656</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F54" s="27">
         <v>46147.369606481479</v>
       </c>
       <c r="G54" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I54" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="27">
@@ -2744,28 +2741,28 @@
         <v>VNMI1040233560</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D55" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F55" s="27">
         <v>46147.380023148151</v>
       </c>
       <c r="G55" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I55" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="27">
@@ -2774,28 +2771,28 @@
         <v>VNMI1040234464</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F56" s="27">
         <v>46148.386967592596</v>
       </c>
       <c r="G56" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H56" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I56" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="27">
@@ -2804,28 +2801,28 @@
         <v>VNMI1040235368</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F57" s="27">
         <v>46148.42863425926</v>
       </c>
       <c r="G57" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I57" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="27">
@@ -2834,28 +2831,28 @@
         <v>VNMI1040236272</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F58" s="27">
         <v>46148.439050925925</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I58" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="27">
@@ -2864,28 +2861,28 @@
         <v>VNMI1040237176</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F59" s="27">
         <v>46148.45988425926</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H59" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I59" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="27">
@@ -2894,28 +2891,28 @@
         <v>VNMI1040238080</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F60" s="27">
         <v>46148.470300925925</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="27">
@@ -2924,28 +2921,28 @@
         <v>VNMI1040238984</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F61" s="27">
         <v>46148.47724537037</v>
       </c>
       <c r="G61" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="27">
@@ -2954,28 +2951,28 @@
         <v>VNMI1040239888</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F62" s="27">
         <v>46148.518912037034</v>
       </c>
       <c r="G62" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H62" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I62" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="27">
@@ -2984,28 +2981,28 @@
         <v>VNMI1040240792</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F63" s="27">
         <v>46148.529328703706</v>
       </c>
       <c r="G63" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H63" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I63" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="27">
@@ -3014,28 +3011,28 @@
         <v>VNMI1040241696</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F64" s="27">
         <v>46148.550162037034</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H64" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I64" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="27">
@@ -3044,28 +3041,28 @@
         <v>VNMI1040242600</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" s="27">
         <v>46148.560578703706</v>
       </c>
       <c r="G65" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I65" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="27">
@@ -3074,28 +3071,28 @@
         <v>VNMI1040243504</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F66" s="27">
         <v>46148.567523148151</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I66" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="27">
@@ -3104,28 +3101,28 @@
         <v>VNMI1040244408</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F67" s="27">
         <v>46148.609189814815</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H67" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="27">
@@ -3134,28 +3131,28 @@
         <v>VNMI1040245312</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F68" s="27">
         <v>46148.619606481479</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H68" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I68" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="27">
@@ -3164,28 +3161,28 @@
         <v>VNMI1040246216</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F69" s="27">
         <v>46148.640439814815</v>
       </c>
       <c r="G69" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H69" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I69" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="27">
@@ -3194,28 +3191,28 @@
         <v>VNMI1040247120</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F70" s="27">
         <v>46148.650856481479</v>
       </c>
       <c r="G70" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I70" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="27">
@@ -3224,28 +3221,28 @@
         <v>VNMI1040248024</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F71" s="27">
         <v>46148.657800925925</v>
       </c>
       <c r="G71" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I71" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="27">
@@ -3254,28 +3251,28 @@
         <v>VNMI1040248928</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F72" s="27">
         <v>46149.699467592596</v>
       </c>
       <c r="G72" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I72" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="27">
@@ -3284,28 +3281,28 @@
         <v>VNMI1040249832</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F73" s="27">
         <v>46149.70988425926</v>
       </c>
       <c r="G73" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H73" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I73" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="27">
@@ -3314,28 +3311,28 @@
         <v>VNMI1040250736</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F74" s="27">
         <v>46149.730717592596</v>
       </c>
       <c r="G74" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I74" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="27">
@@ -3344,28 +3341,28 @@
         <v>VNMI1040251640</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F75" s="27">
         <v>46149.74113425926</v>
       </c>
       <c r="G75" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H75" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H75" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I75" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="27">
@@ -3374,28 +3371,28 @@
         <v>VNMI1040252544</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F76" s="27">
         <v>46149.748078703706</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H76" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I76" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="27">
@@ -3404,28 +3401,28 @@
         <v>VNMI1040253448</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F77" s="27">
         <v>46149.78974537037</v>
       </c>
       <c r="G77" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I77" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="27">
@@ -3434,28 +3431,28 @@
         <v>VNMI1040254352</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" s="27">
         <v>46149.800162037034</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H78" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I78" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="27">
@@ -3464,28 +3461,28 @@
         <v>VNMI1040255256</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" s="27">
         <v>46149.82099537037</v>
       </c>
       <c r="G79" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H79" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I79" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="27">
@@ -3494,28 +3491,28 @@
         <v>VNMI1040256160</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F80" s="27">
         <v>46149.831412037034</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H80" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I80" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="27">
@@ -3524,28 +3521,28 @@
         <v>VNMI1040257064</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F81" s="27">
         <v>46149.838356481479</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I81" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="27">
@@ -3554,28 +3551,28 @@
         <v>VNMI1040257968</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F82" s="27">
         <v>46150.880023148151</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H82" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I82" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="27">
@@ -3584,28 +3581,28 @@
         <v>VNMI1040258872</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F83" s="27">
         <v>46150.890439814815</v>
       </c>
       <c r="G83" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H83" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I83" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="27">
@@ -3614,28 +3611,28 @@
         <v>VNMI1040259776</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F84" s="27">
         <v>46150.911273148151</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="27">
@@ -3644,28 +3641,28 @@
         <v>VNMI1040260680</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F85" s="27">
         <v>46150.921689814815</v>
       </c>
       <c r="G85" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H85" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I85" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="27">
@@ -3674,28 +3671,28 @@
         <v>VNMI1040261584</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F86" s="27">
         <v>46150.92863425926</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I86" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="27">
@@ -3704,28 +3701,28 @@
         <v>VNMI1040262488</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F87" s="27">
         <v>46150.970300925925</v>
       </c>
       <c r="G87" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I87" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="27">
@@ -3734,28 +3731,28 @@
         <v>VNMI1040263392</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" s="27">
         <v>46151.980717592596</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I88" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="27">
@@ -3764,28 +3761,28 @@
         <v>VNMI1040264296</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" s="27">
         <v>46152.001550925925</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H89" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I89" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="27">
@@ -3794,28 +3791,28 @@
         <v>VNMI1040265200</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F90" s="27">
         <v>46152.011967592596</v>
       </c>
       <c r="G90" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H90" s="26" t="s">
-        <v>26</v>
-      </c>
       <c r="I90" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="27">
@@ -3824,28 +3821,28 @@
         <v>VNMI1040266104</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F91" s="27">
         <v>46152.018912037034</v>
       </c>
       <c r="G91" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H91" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I91" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="27">
@@ -3854,28 +3851,28 @@
         <v>VNMI1040267008</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F92" s="27">
         <v>46152.060578703706</v>
       </c>
       <c r="G92" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I92" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="27">
@@ -3884,28 +3881,28 @@
         <v>VNMI1040267912</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D93" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F93" s="27">
         <v>46153.07099537037</v>
       </c>
       <c r="G93" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H93" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I93" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="27">
@@ -3914,28 +3911,28 @@
         <v>VNMI1040268816</v>
       </c>
       <c r="B94" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F94" s="27">
         <v>46153.091828703706</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H94" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I94" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="27">
@@ -3944,28 +3941,28 @@
         <v>VNMI1040269720</v>
       </c>
       <c r="B95" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D95" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F95" s="27">
         <v>46153.10224537037</v>
       </c>
       <c r="G95" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H95" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I95" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3987,38 +3984,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="16" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" s="16" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
     </row>
     <row r="3" spans="1:5" s="17" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="37" t="s">
+      <c r="A3" s="35"/>
+      <c r="B3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="46"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="37"/>
     </row>
     <row r="4" spans="1:5" s="17" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A4" s="45"/>
-      <c r="B4" s="43" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="47"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="38"/>
     </row>
     <row r="5" spans="1:5" ht="34.5">
       <c r="A5" s="18" t="str">
@@ -4026,14 +4023,14 @@
         <v>RJ07GE8948</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="19" t="str">
         <f>Sheet1!A2</f>
         <v>VNMI1040185648</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="20">
         <f>Sheet1!F2</f>
@@ -4041,16 +4038,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="12">
         <f>E5</f>
         <v>46142.435578703706</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="7" t="str">
         <f>Sheet1!B2</f>
@@ -4058,16 +4055,16 @@
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="47"/>
       <c r="C7" s="13">
         <f>C6</f>
         <v>46142.435578703706</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="8" t="e">
         <f>Sheet1!#REF!</f>
@@ -4075,58 +4072,58 @@
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="32"/>
+      <c r="A8" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="40"/>
       <c r="C8" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="8">
         <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="32"/>
+      <c r="A9" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="40"/>
       <c r="C9" s="8"/>
       <c r="D9" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="32"/>
+      <c r="A10" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="40"/>
       <c r="C10" s="8"/>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="32"/>
+      <c r="A11" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="40"/>
       <c r="C11" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="32"/>
+      <c r="A12" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="40"/>
       <c r="C12" s="14" t="str">
         <f>Sheet1!G2</f>
         <v>MasonaryStone (Gitti)</v>
@@ -4135,10 +4132,10 @@
       <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A13" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="32"/>
+      <c r="A13" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="40"/>
       <c r="C13" s="8" t="str">
         <f>Sheet1!H2</f>
         <v>46.5 MT</v>
@@ -4147,10 +4144,10 @@
       <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A14" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="32"/>
+      <c r="A14" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="40"/>
       <c r="C14" s="8">
         <v>13.55</v>
       </c>
@@ -4158,37 +4155,46 @@
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A15" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="49"/>
+      <c r="A15" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="42"/>
       <c r="C15" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" ht="160.5" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="41"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="32"/>
     </row>
     <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
+      <c r="A17" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
     </row>
     <row r="19" spans="1:5" ht="16.5">
       <c r="A19" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="A17:E17"/>
@@ -4199,15 +4205,6 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="69" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shank\Desktop\MY PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4821E991-BC83-42EC-8E0E-23D70B332239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674FE9BF-9889-46FE-A392-61BA46F49AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CD8F0B71-79B1-40C9-A2D5-894CEF5A2152}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="39">
   <si>
     <t>VNMI1040185648</t>
   </si>
@@ -140,6 +140,33 @@
   </si>
   <si>
     <t>sklf1040268955</t>
+  </si>
+  <si>
+    <t>SHANKAR</t>
+  </si>
+  <si>
+    <t>RAMAVTAR</t>
+  </si>
+  <si>
+    <t>DHADHERU</t>
+  </si>
+  <si>
+    <t>PRADEEP NAGAR</t>
+  </si>
+  <si>
+    <t>GUDDI DEVI CIRCLE</t>
+  </si>
+  <si>
+    <t>MADAN CONSTRRUCTION</t>
+  </si>
+  <si>
+    <t>GHEWAR</t>
+  </si>
+  <si>
+    <t>RUKHMA</t>
+  </si>
+  <si>
+    <t>POOJA</t>
   </si>
 </sst>
 </file>
@@ -582,10 +609,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F94DEA-726A-4004-8BFE-9C5DC5168EED}">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultColWidth="17.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="17.7109375" style="1"/>
+    <col min="1" max="1" width="22.42578125" style="1" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" style="1"/>
     <col min="5" max="5" width="17.7109375" style="3"/>
     <col min="6" max="6" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="17.7109375" style="1"/>
@@ -2601,7 +2629,7 @@
     </row>
     <row r="68" spans="1:9" ht="27" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="str">
-        <f t="shared" ref="A68:A95" si="1">LEFT(A67,LEN(A67)-10)&amp;TEXT(RIGHT(A67,10)+904,"0000000000")</f>
+        <f t="shared" ref="A68:A94" si="1">LEFT(A67,LEN(A67)-10)&amp;TEXT(RIGHT(A67,10)+904,"0000000000")</f>
         <v>VNMI1040245312</v>
       </c>
       <c r="B68" s="7" t="s">
@@ -3436,6 +3464,35 @@
       </c>
       <c r="I95" s="7" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
